--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.98581864723748</v>
+        <v>5.197695530176091</v>
       </c>
       <c r="D2" t="n">
-        <v>32.10749063029967</v>
+        <v>5.217467227423697</v>
       </c>
       <c r="E2" t="n">
-        <v>10.94121223183316</v>
+        <v>1.777946987672889</v>
       </c>
       <c r="F2" t="n">
-        <v>11.03286031135559</v>
+        <v>1.792839800595284</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.74467783966526</v>
+        <v>6.296010148945604</v>
       </c>
       <c r="D3" t="n">
-        <v>38.87483433097109</v>
+        <v>6.317160578782802</v>
       </c>
       <c r="E3" t="n">
-        <v>10.94121223183316</v>
+        <v>1.777946987672889</v>
       </c>
       <c r="F3" t="n">
-        <v>11.03286031135559</v>
+        <v>1.792839800595284</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.0674656760927</v>
+        <v>9.598463172365065</v>
       </c>
       <c r="D4" t="n">
-        <v>59.22243207601054</v>
+        <v>9.623645212351713</v>
       </c>
       <c r="E4" t="n">
-        <v>10.94121223183316</v>
+        <v>1.777946987672889</v>
       </c>
       <c r="F4" t="n">
-        <v>11.03286031135559</v>
+        <v>1.792839800595284</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.17390046501272</v>
+        <v>4.578258825564568</v>
       </c>
       <c r="D5" t="n">
-        <v>28.00863290862314</v>
+        <v>4.55140284765126</v>
       </c>
       <c r="E5" t="n">
-        <v>10.94121223183316</v>
+        <v>1.777946987672889</v>
       </c>
       <c r="F5" t="n">
-        <v>11.03286031135559</v>
+        <v>1.792839800595284</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.33350679193101</v>
+        <v>5.41669485368879</v>
       </c>
       <c r="D6" t="n">
-        <v>33.17314906183716</v>
+        <v>5.390636722548538</v>
       </c>
       <c r="E6" t="n">
-        <v>10.94121223183316</v>
+        <v>1.777946987672889</v>
       </c>
       <c r="F6" t="n">
-        <v>11.03286031135559</v>
+        <v>1.792839800595284</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
